--- a/data/trending_integrated_20260917_09.xlsx
+++ b/data/trending_integrated_20260917_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3630</v>
+        <v>4300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+3.12%</t>
+          <t>'+11.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.85</v>
+        <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G2" t="n">
-        <v>128</v>
+        <v>307</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3520</v>
+        <v>3840</v>
       </c>
       <c r="K2" t="n">
-        <v>3730</v>
+        <v>4170</v>
       </c>
       <c r="L2" t="n">
-        <v>3750</v>
+        <v>4500</v>
       </c>
       <c r="M2" t="n">
-        <v>3615</v>
+        <v>4000</v>
       </c>
       <c r="N2" t="n">
-        <v>3.11</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>636178635</v>
+        <v>54514633433</v>
       </c>
       <c r="P2" t="n">
-        <v>16110</v>
+        <v>6900</v>
       </c>
       <c r="Q2" t="n">
-        <v>2300</v>
+        <v>1738</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>내부거래 의혹 및 상장폐지 가능성 언급으로 인한 부정적 심리 확산. 급락 가능성 제기.</t>
+          <t>거래량 급증 및 매수세 유입 언급. 소프트뱅크 투자 기대감과 텐버거 달성 가능성 논의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상장폐지', '의혹', '폭락']</t>
+          <t>['거래량', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16380</v>
+        <v>255500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+0.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>692</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>371</v>
       </c>
       <c r="G3" t="n">
-        <v>547</v>
+        <v>2894</v>
       </c>
       <c r="H3" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="K3" t="n">
-        <v>16200</v>
+        <v>257000</v>
       </c>
       <c r="L3" t="n">
-        <v>16590</v>
+        <v>259000</v>
       </c>
       <c r="M3" t="n">
-        <v>16120</v>
+        <v>254500</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O3" t="n">
-        <v>22814096560</v>
+        <v>289296338500</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q3" t="n">
-        <v>1272</v>
+        <v>77100</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등 및 세계적인 통신 장비 부족 현상이 긍정적 요인으로 작용. 2만원 돌파 기대.</t>
+          <t>미국 금리 인상 및 정치적 불확실성 언급. 메모리 수요와 금리 인상 간의 관계에 대한 논의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '호재']</t>
+          <t>['금리인상', '메모리수요', '불확실성']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1775000</v>
+        <v>84400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'+0.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>415</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>2804</v>
+        <v>367</v>
       </c>
       <c r="H4" t="n">
-        <v>50.2</v>
+        <v>23.27</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1759000</v>
+        <v>83800</v>
       </c>
       <c r="K4" t="n">
-        <v>1770000</v>
+        <v>84700</v>
       </c>
       <c r="L4" t="n">
-        <v>1785000</v>
+        <v>85200</v>
       </c>
       <c r="M4" t="n">
-        <v>1768000</v>
+        <v>84100</v>
       </c>
       <c r="N4" t="n">
-        <v>50.2</v>
+        <v>23.37</v>
       </c>
       <c r="O4" t="n">
-        <v>306375660000</v>
+        <v>18434837950</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q4" t="n">
-        <v>333000</v>
+        <v>57000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금리 인상 종결로 인한 불확실성 해소와 미국 반도체 주 강세가 긍정적 전망을 뒷받침. 메모리 공급 부족 심화 예상.</t>
+          <t>AI 투자와 전력 부족 문제 언급. FOMC 악재 해소 후 금리 인상 영향 및 대미 투자에 대한 소고.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '공급부족']</t>
+          <t>['AI', '금리인상', '전력']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13680</v>
+        <v>3535</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K5" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L5" t="n">
-        <v>13730</v>
+        <v>3750</v>
       </c>
       <c r="M5" t="n">
-        <v>13410</v>
+        <v>3510</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O5" t="n">
-        <v>1745294880</v>
+        <v>2167624266</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,27 +902,303 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유가 하락세 지속 및 미 증시 하락 영향으로 부정적 전망. 유가 변동성에 따른 등락 예상.</t>
+          <t>단기 차익 실현 및 폭락 가능성 언급. FOMC 불확실성 해소 후 시장 반응에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['차익실현', '폭락', 'FOMC']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>424870</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1748000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-0.63%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>434</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2690</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1759000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1770000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1747000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>620144321000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>333000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>금리 인상 종결로 인한 불확실성 해소와 미국 반도체 주 강세가 긍정적 전망을 뒷받침. 메모리 공급 부족 심화 예상.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['금리인상', '반도체', '공급부족']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>15950</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-0.93%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>94</v>
+      </c>
+      <c r="F7" t="n">
+        <v>64</v>
+      </c>
+      <c r="G7" t="n">
+        <v>612</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>16100</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16200</v>
+      </c>
+      <c r="L7" t="n">
+        <v>16590</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15560</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O7" t="n">
+        <v>76280714615</v>
+      </c>
+      <c r="P7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>미국 광통신 종목 급등 영향 언급. 세계적 통신 장비 부족 현상과 2만원 목표가 제시.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['광통신', '통신장비', '호재']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13670</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-2.15%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" t="n">
+        <v>38</v>
+      </c>
+      <c r="G8" t="n">
+        <v>165</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>13970</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L8" t="n">
+        <v>13890</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13410</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4086939345</v>
+      </c>
+      <c r="P8" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>겨울 대비 유가 전망 및 미국 중간선거 관련 유가 변동성 언급. 유가 등락 패턴 분석.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>['유가', '흥구석유', '전망']</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['유가', '겨울', '중간선거']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>7</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>024060</t>
         </is>

--- a/data/trending_integrated_20260917_09.xlsx
+++ b/data/trending_integrated_20260917_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4300</v>
+        <v>11450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+11.98%</t>
+          <t>'+14.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.08</v>
+        <v>0.58</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>307</v>
+        <v>52</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3840</v>
+        <v>9970</v>
       </c>
       <c r="K2" t="n">
-        <v>4170</v>
+        <v>10280</v>
       </c>
       <c r="L2" t="n">
-        <v>4500</v>
+        <v>11750</v>
       </c>
       <c r="M2" t="n">
-        <v>4000</v>
+        <v>10250</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>0.67</v>
       </c>
       <c r="O2" t="n">
-        <v>54514633433</v>
+        <v>82533345205</v>
       </c>
       <c r="P2" t="n">
-        <v>6900</v>
+        <v>15960</v>
       </c>
       <c r="Q2" t="n">
-        <v>1738</v>
+        <v>3500</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>114000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>거래량 급증 및 매수세 유입 언급. 소프트뱅크 투자 기대감과 텐버거 달성 가능성 논의.</t>
+          <t>낙태약 도입 및 탈모 치료 관련 기대감과 함께 치매 테마 영향에 대한 분석. 개인 매도 물량 확인 및 2만원 목표 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['거래량', '소프트뱅크', '텐버거']</t>
+          <t>['낙태약', '탈모치료', '치매테마']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>255500</v>
+        <v>4215</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.79%</t>
+          <t>'+9.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>692</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>371</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>2894</v>
+        <v>345</v>
       </c>
       <c r="H3" t="n">
-        <v>46.52</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>253500</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
-        <v>257000</v>
+        <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>259000</v>
+        <v>4500</v>
       </c>
       <c r="M3" t="n">
-        <v>254500</v>
+        <v>4000</v>
       </c>
       <c r="N3" t="n">
-        <v>46.56</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>289296338500</v>
+        <v>65623679964</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>77100</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-74000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 금리 인상 및 정치적 불확실성 언급. 메모리 수요와 금리 인상 간의 관계에 대한 논의.</t>
+          <t>소프트뱅크 손정의 관련 인수 기대감과 함께 카카오 인수설 및 10배 상승 전망. 1만원 이하 매도 불가 입장.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['금리인상', '메모리수요', '불확실성']</t>
+          <t>['소프트뱅크', '카카오인수', '텐버거']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84400</v>
+        <v>16380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.72%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1</v>
+        <v>2.93</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>367</v>
+        <v>652</v>
       </c>
       <c r="H4" t="n">
-        <v>23.27</v>
+        <v>4.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>83800</v>
+        <v>16100</v>
       </c>
       <c r="K4" t="n">
-        <v>84700</v>
+        <v>16200</v>
       </c>
       <c r="L4" t="n">
-        <v>85200</v>
+        <v>16590</v>
       </c>
       <c r="M4" t="n">
-        <v>84100</v>
+        <v>15560</v>
       </c>
       <c r="N4" t="n">
-        <v>23.37</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>18434837950</v>
+        <v>104549559965</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-208000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 투자와 전력 부족 문제 언급. FOMC 악재 해소 후 금리 인상 영향 및 대미 투자에 대한 소고.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께 2만원 목표 제시. 세계적 통신 장비 부족 현상 호재 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '금리인상', '전력']</t>
+          <t>['광통신', '루멘텀', '통신장비']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3535</v>
+        <v>84500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.85</v>
+        <v>-0.1</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>150</v>
+        <v>388</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>23.27</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3520</v>
+        <v>83800</v>
       </c>
       <c r="K5" t="n">
-        <v>3730</v>
+        <v>84700</v>
       </c>
       <c r="L5" t="n">
-        <v>3750</v>
+        <v>85200</v>
       </c>
       <c r="M5" t="n">
-        <v>3510</v>
+        <v>84100</v>
       </c>
       <c r="N5" t="n">
-        <v>3.11</v>
+        <v>23.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2167624266</v>
+        <v>24307138700</v>
       </c>
       <c r="P5" t="n">
-        <v>16110</v>
+        <v>139200</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>57000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-61000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기 차익 실현 및 폭락 가능성 언급. FOMC 불확실성 해소 후 시장 반응에 대한 부정적 전망.</t>
+          <t>AI 투자와 전력 부족 문제 언급. FOMC 악재 해소 후 금리 인상 영향 및 대미 투자에 대한 소고.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['차익실현', '폭락', 'FOMC']</t>
+          <t>['AI', '금리인상', '전력']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1748000</v>
+        <v>3530</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.63%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>434</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>2690</v>
+        <v>160</v>
       </c>
       <c r="H6" t="n">
-        <v>50.2</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1759000</v>
+        <v>3520</v>
       </c>
       <c r="K6" t="n">
-        <v>1770000</v>
+        <v>3730</v>
       </c>
       <c r="L6" t="n">
-        <v>1785000</v>
+        <v>3750</v>
       </c>
       <c r="M6" t="n">
-        <v>1747000</v>
+        <v>3510</v>
       </c>
       <c r="N6" t="n">
-        <v>50.2</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
-        <v>620144321000</v>
+        <v>2991266111</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>16110</v>
       </c>
       <c r="Q6" t="n">
-        <v>333000</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-228000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>금리 인상 종결로 인한 불확실성 해소와 미국 반도체 주 강세가 긍정적 전망을 뒷받침. 메모리 공급 부족 심화 예상.</t>
+          <t>상장폐지 우려 및 내부거래자 의혹 제기. 급락 및 차익 실현 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '공급부족']</t>
+          <t>['상장폐지', '내부거래', '폭락']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15950</v>
+        <v>254000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>719</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>395</v>
       </c>
       <c r="G7" t="n">
-        <v>612</v>
+        <v>2993</v>
       </c>
       <c r="H7" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="K7" t="n">
-        <v>16200</v>
+        <v>257000</v>
       </c>
       <c r="L7" t="n">
-        <v>16590</v>
+        <v>259000</v>
       </c>
       <c r="M7" t="n">
-        <v>15560</v>
+        <v>253500</v>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O7" t="n">
-        <v>76280714615</v>
+        <v>406101271250</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1272</v>
+        <v>77100</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신 종목 급등 영향 언급. 세계적 통신 장비 부족 현상과 2만원 목표가 제시.</t>
+          <t>미국 금리 인상 및 정치적 불확실성 언급. 메모리 수요와 금리 인상 간의 관계에 대한 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '호재']</t>
+          <t>['금리인상', '메모리수요', '불확실성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,97 +1108,189 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13670</v>
+        <v>1747000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>446</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>2543</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>50.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13970</v>
+        <v>1759000</v>
       </c>
       <c r="K8" t="n">
-        <v>13450</v>
+        <v>1770000</v>
       </c>
       <c r="L8" t="n">
-        <v>13890</v>
+        <v>1785000</v>
       </c>
       <c r="M8" t="n">
-        <v>13410</v>
+        <v>1742000</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4086939345</v>
+        <v>814504181500</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>333000</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-85000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>겨울 대비 유가 전망 및 미국 중간선거 관련 유가 변동성 언급. 유가 등락 패턴 분석.</t>
+          <t>금리 인상 종결로 인한 불확실성 해소와 미국 반도체 주 강세가 긍정적 전망을 뒷받침. 메모리 공급 부족 심화 예상.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['금리인상', '반도체', '공급부족']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13830</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-1.00%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" t="n">
+        <v>54</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>174</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>13970</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13890</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13410</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5684749400</v>
+      </c>
+      <c r="P9" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>유가 상승 및 겨울 도래에 따른 긍정적 전망과 달리, 유가 하락 및 미주 증시 약세 영향 분석. 단기적 등락 반복 패턴 예상.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
         <v>0.2</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>['유가', '겨울', '중간선거']</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['유가', '두바이유', 'WTI']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>7</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>024060</t>
         </is>

--- a/data/trending_integrated_20260917_09.xlsx
+++ b/data/trending_integrated_20260917_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11450</v>
+        <v>4405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.84%</t>
+          <t>'+14.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.58</v>
+        <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>381</v>
       </c>
       <c r="H2" t="n">
-        <v>1.25</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9970</v>
+        <v>3840</v>
       </c>
       <c r="K2" t="n">
-        <v>10280</v>
+        <v>4170</v>
       </c>
       <c r="L2" t="n">
-        <v>11750</v>
+        <v>4500</v>
       </c>
       <c r="M2" t="n">
-        <v>10250</v>
+        <v>4000</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>82533345205</v>
+        <v>80030657148</v>
       </c>
       <c r="P2" t="n">
-        <v>15960</v>
+        <v>6900</v>
       </c>
       <c r="Q2" t="n">
-        <v>3500</v>
+        <v>1738</v>
       </c>
       <c r="R2" t="n">
-        <v>114000</v>
+        <v>-74000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>낙태약 도입 및 탈모 치료 관련 기대감과 함께 치매 테마 영향에 대한 분석. 개인 매도 물량 확인 및 2만원 목표 제시.</t>
+          <t>카카오 인수 및 소프트뱅크 투자 관련 루머 기반 급등 기대. 10배 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '치매테마']</t>
+          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4215</v>
+        <v>11000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.77%</t>
+          <t>'+10.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.08</v>
+        <v>0.58</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>345</v>
+        <v>59</v>
       </c>
       <c r="H3" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3840</v>
+        <v>9970</v>
       </c>
       <c r="K3" t="n">
-        <v>4170</v>
+        <v>10280</v>
       </c>
       <c r="L3" t="n">
-        <v>4500</v>
+        <v>11750</v>
       </c>
       <c r="M3" t="n">
-        <v>4000</v>
+        <v>10250</v>
       </c>
       <c r="N3" t="n">
-        <v>1.03</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>65623679964</v>
+        <v>109785518390</v>
       </c>
       <c r="P3" t="n">
-        <v>6900</v>
+        <v>15960</v>
       </c>
       <c r="Q3" t="n">
-        <v>1738</v>
+        <v>3500</v>
       </c>
       <c r="R3" t="n">
-        <v>-74000</v>
+        <v>114000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>소프트뱅크 손정의 관련 인수 기대감과 함께 카카오 인수설 및 10배 상승 전망. 1만원 이하 매도 불가 입장.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감 언급. 개미 매도 후 개인 물량 털림.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['소프트뱅크', '카카오인수', '텐버거']</t>
+          <t>['낙태약', '탈모 치료제']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16380</v>
+        <v>3725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+6.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.93</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>652</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>4.88</v>
+        <v>8.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16100</v>
+        <v>3500</v>
       </c>
       <c r="K4" t="n">
-        <v>16200</v>
+        <v>3590</v>
       </c>
       <c r="L4" t="n">
-        <v>16590</v>
+        <v>4130</v>
       </c>
       <c r="M4" t="n">
-        <v>15560</v>
+        <v>3550</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>8.06</v>
       </c>
       <c r="O4" t="n">
-        <v>104549559965</v>
+        <v>45412744220</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>19950</v>
       </c>
       <c r="Q4" t="n">
-        <v>1272</v>
+        <v>1913</v>
       </c>
       <c r="R4" t="n">
-        <v>-208000</v>
+        <v>-55000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께 2만원 목표 제시. 세계적 통신 장비 부족 현상 호재 분석.</t>
+          <t>단기 급등 후 하락세. 개인 매수세와 외국인 매도세 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '통신장비']</t>
+          <t>['급등', '개인매수', '외국인매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84500</v>
+        <v>16340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.84%</t>
+          <t>'+1.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1</v>
+        <v>2.93</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
-        <v>388</v>
+        <v>682</v>
       </c>
       <c r="H5" t="n">
-        <v>23.27</v>
+        <v>4.88</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>83800</v>
+        <v>16100</v>
       </c>
       <c r="K5" t="n">
-        <v>84700</v>
+        <v>16200</v>
       </c>
       <c r="L5" t="n">
-        <v>85200</v>
+        <v>16750</v>
       </c>
       <c r="M5" t="n">
-        <v>84100</v>
+        <v>15560</v>
       </c>
       <c r="N5" t="n">
-        <v>23.37</v>
+        <v>1.95</v>
       </c>
       <c r="O5" t="n">
-        <v>24307138700</v>
+        <v>157743517300</v>
       </c>
       <c r="P5" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>-61000</v>
+        <v>-208000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 투자와 전력 부족 문제 언급. FOMC 악재 해소 후 금리 인상 영향 및 대미 투자에 대한 소고.</t>
+          <t>미국 광통신주 급등에 따른 국내 광통신주 동반 상승 기대. 통신장비 부족 호재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '금리인상', '전력']</t>
+          <t>['광통신', '통신장비', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3530</v>
+        <v>85000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+1.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.85</v>
+        <v>-0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>407</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26</v>
+        <v>23.27</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3520</v>
+        <v>83800</v>
       </c>
       <c r="K6" t="n">
-        <v>3730</v>
+        <v>84700</v>
       </c>
       <c r="L6" t="n">
-        <v>3750</v>
+        <v>85500</v>
       </c>
       <c r="M6" t="n">
-        <v>3510</v>
+        <v>84100</v>
       </c>
       <c r="N6" t="n">
-        <v>3.11</v>
+        <v>23.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2991266111</v>
+        <v>32294487150</v>
       </c>
       <c r="P6" t="n">
-        <v>16110</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>-228000</v>
+        <v>-61000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상장폐지 우려 및 내부거래자 의혹 제기. 급락 및 차익 실현 가능성 언급.</t>
+          <t>금리 인상 악재 해소 및 AI 관련 전력 수요 증가 전망. 원전 관련주 연계 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['상장폐지', '내부거래', '폭락']</t>
+          <t>['금리인상', 'AI', '원전']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254000</v>
+        <v>18630</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>719</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>395</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>2993</v>
+        <v>127</v>
       </c>
       <c r="H7" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>253500</v>
+        <v>18570</v>
       </c>
       <c r="K7" t="n">
-        <v>257000</v>
+        <v>18740</v>
       </c>
       <c r="L7" t="n">
-        <v>259000</v>
+        <v>18900</v>
       </c>
       <c r="M7" t="n">
-        <v>253500</v>
+        <v>18580</v>
       </c>
       <c r="N7" t="n">
-        <v>46.56</v>
+        <v>10.64</v>
       </c>
       <c r="O7" t="n">
-        <v>406101271250</v>
+        <v>17837036495</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>5000</v>
+        <v>-58000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 금리 인상 및 정치적 불확실성 언급. 메모리 수요와 금리 인상 간의 관계에 대한 논의.</t>
+          <t>금리 인상 속 대규모 수주에도 부진한 주가. 대차해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['금리인상', '메모리수요', '불확실성']</t>
+          <t>['금리인상', '수주', '대차해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1747000</v>
+        <v>3517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>2543</v>
+        <v>177</v>
       </c>
       <c r="H8" t="n">
-        <v>50.2</v>
+        <v>2.26</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1759000</v>
+        <v>3520</v>
       </c>
       <c r="K8" t="n">
-        <v>1770000</v>
+        <v>3730</v>
       </c>
       <c r="L8" t="n">
-        <v>1785000</v>
+        <v>3750</v>
       </c>
       <c r="M8" t="n">
-        <v>1742000</v>
+        <v>3510</v>
       </c>
       <c r="N8" t="n">
-        <v>50.2</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>814504181500</v>
+        <v>3252557025</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>16110</v>
       </c>
       <c r="Q8" t="n">
-        <v>333000</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>-85000</v>
+        <v>-228000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>금리 인상 종결로 인한 불확실성 해소와 미국 반도체 주 강세가 긍정적 전망을 뒷받침. 메모리 공급 부족 심화 예상.</t>
+          <t>상장 폐지 가능성 언급 및 급락세 지속. 차익 실현 매물 출회.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '공급부족']</t>
+          <t>['상장폐지', '급락', '차익실현']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,375 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13830</v>
+        <v>252750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>786</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>428</v>
       </c>
       <c r="G9" t="n">
-        <v>174</v>
+        <v>3143</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01</v>
+        <v>46.52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13970</v>
+        <v>253500</v>
       </c>
       <c r="K9" t="n">
-        <v>13450</v>
+        <v>257000</v>
       </c>
       <c r="L9" t="n">
-        <v>13890</v>
+        <v>259000</v>
       </c>
       <c r="M9" t="n">
-        <v>13410</v>
+        <v>252500</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="O9" t="n">
-        <v>5684749400</v>
+        <v>508657100250</v>
       </c>
       <c r="P9" t="n">
-        <v>36200</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>8920</v>
+        <v>77100</v>
       </c>
       <c r="R9" t="n">
-        <v>73000</v>
+        <v>5000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유가 상승 및 겨울 도래에 따른 긍정적 전망과 달리, 유가 하락 및 미주 증시 약세 영향 분석. 단기적 등락 반복 패턴 예상.</t>
+          <t>미국 금리 인상 및 정치적 불확실성 언급. 메모리 수요와 금리 인상 간의 관계에 대한 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['금리인상', '메모리수요', '불확실성']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>13920</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-0.36%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" t="n">
+        <v>189</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>13970</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L10" t="n">
+        <v>13960</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13410</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7034366740</v>
+      </c>
+      <c r="P10" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R10" t="n">
+        <v>73000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>유가 등락에 따른 변동성 확대. 겨울철 유가 상승 및 전쟁 관련 기대와 하락 우려 공존.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
         <v>0.2</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['유가', '두바이유', 'WTI']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['유가', '겨울', '전쟁']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>7</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8390</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-0.94%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>47</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>101</v>
+      </c>
+      <c r="H11" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>8470</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8470</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8510</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8370</v>
+      </c>
+      <c r="N11" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4125165650</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>중국 디스플레이 경쟁력 약화 및 높은 부채 비율 언급. 외인 매도세 지속.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['디스플레이', '중국', '부채']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1736500</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-1.28%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>800</v>
+      </c>
+      <c r="F12" t="n">
+        <v>461</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2267</v>
+      </c>
+      <c r="H12" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1759000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1770000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1736000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>993429360500</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>333000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-85000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 금리 인상 불확실성 해소 기대 속 반도체 부족 심화 전망. 금리 인상 후 폭락 예상도.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['금리인상', '반도체', 'ADR']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260917_09.xlsx
+++ b/data/trending_integrated_20260917_09.xlsx
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4405</v>
+        <v>10690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.71%</t>
+          <t>'+7.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.08</v>
+        <v>0.58</v>
       </c>
       <c r="E2" t="n">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3840</v>
+        <v>9970</v>
       </c>
       <c r="K2" t="n">
-        <v>4170</v>
+        <v>10280</v>
       </c>
       <c r="L2" t="n">
-        <v>4500</v>
+        <v>11750</v>
       </c>
       <c r="M2" t="n">
-        <v>4000</v>
+        <v>10250</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>0.67</v>
       </c>
       <c r="O2" t="n">
-        <v>80030657148</v>
+        <v>129420646385</v>
       </c>
       <c r="P2" t="n">
-        <v>6900</v>
+        <v>15960</v>
       </c>
       <c r="Q2" t="n">
-        <v>1738</v>
+        <v>3500</v>
       </c>
       <c r="R2" t="n">
-        <v>-74000</v>
+        <v>114000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오 인수 및 소프트뱅크 투자 관련 루머 기반 급등 기대. 10배 상승 가능성 언급.</t>
+          <t>낙태약 도입 및 탈모 치료 관련 기대감, 치매 테마 영향 가능성 언급. 그러나 개인 매도 및 신뢰 부족 지적.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
+          <t>['낙태약', '탈모치료', '치매테마']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11000</v>
+        <v>3700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.33%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.58</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H3" t="n">
-        <v>1.25</v>
+        <v>8.01</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9970</v>
+        <v>3500</v>
       </c>
       <c r="K3" t="n">
-        <v>10280</v>
+        <v>3590</v>
       </c>
       <c r="L3" t="n">
-        <v>11750</v>
+        <v>4130</v>
       </c>
       <c r="M3" t="n">
-        <v>10250</v>
+        <v>3550</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>8.06</v>
       </c>
       <c r="O3" t="n">
-        <v>109785518390</v>
+        <v>47805819032</v>
       </c>
       <c r="P3" t="n">
-        <v>15960</v>
+        <v>19950</v>
       </c>
       <c r="Q3" t="n">
-        <v>3500</v>
+        <v>1913</v>
       </c>
       <c r="R3" t="n">
-        <v>114000</v>
+        <v>-55000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 기대감 언급. 개미 매도 후 개인 물량 털림.</t>
+          <t>미래 벤처 투자 관련 언급 있으나, 주가 하락 및 매물량 출회로 인한 부정적 전망. 희망 없는 종목으로 평가.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모 치료제']</t>
+          <t>['미래벤처', '주가하락', '매물량']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3725</v>
+        <v>4015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.43%</t>
+          <t>'+4.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>443</v>
       </c>
       <c r="H4" t="n">
-        <v>8.01</v>
+        <v>0.95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3500</v>
+        <v>3840</v>
       </c>
       <c r="K4" t="n">
-        <v>3590</v>
+        <v>4170</v>
       </c>
       <c r="L4" t="n">
-        <v>4130</v>
+        <v>4500</v>
       </c>
       <c r="M4" t="n">
-        <v>3550</v>
+        <v>3990</v>
       </c>
       <c r="N4" t="n">
-        <v>8.06</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>45412744220</v>
+        <v>97392125706</v>
       </c>
       <c r="P4" t="n">
-        <v>19950</v>
+        <v>6900</v>
       </c>
       <c r="Q4" t="n">
-        <v>1913</v>
+        <v>1738</v>
       </c>
       <c r="R4" t="n">
-        <v>-55000</v>
+        <v>-74000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락세. 개인 매수세와 외국인 매도세 혼재.</t>
+          <t>소프트뱅크 인수 및 카카오 인수 가능성에 대한 높은 기대감. 텐버거 목표 제시 및 거래량 잠김 현상 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['급등', '개인매수', '외국인매도']</t>
+          <t>['소프트뱅크', '카카오', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16340</v>
+        <v>85650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.49%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.93</v>
+        <v>-0.1</v>
       </c>
       <c r="E5" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>682</v>
+        <v>443</v>
       </c>
       <c r="H5" t="n">
-        <v>4.88</v>
+        <v>23.27</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16100</v>
+        <v>83800</v>
       </c>
       <c r="K5" t="n">
-        <v>16200</v>
+        <v>84700</v>
       </c>
       <c r="L5" t="n">
-        <v>16750</v>
+        <v>85900</v>
       </c>
       <c r="M5" t="n">
-        <v>15560</v>
+        <v>84100</v>
       </c>
       <c r="N5" t="n">
-        <v>1.95</v>
+        <v>23.37</v>
       </c>
       <c r="O5" t="n">
-        <v>157743517300</v>
+        <v>41436890350</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R5" t="n">
-        <v>-208000</v>
+        <v>-61000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 국내 광통신주 동반 상승 기대. 통신장비 부족 호재.</t>
+          <t>미국 금리 인상 불확실성 해소 및 AI 시대 전력 수요 증가에 따른 원전 관련 긍정적 전망. 대규모 투자 기대감 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '호재']</t>
+          <t>['원전', '금리인상', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85000</v>
+        <v>16270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1</v>
+        <v>2.93</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G6" t="n">
-        <v>407</v>
+        <v>688</v>
       </c>
       <c r="H6" t="n">
-        <v>23.27</v>
+        <v>4.88</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>83800</v>
+        <v>16100</v>
       </c>
       <c r="K6" t="n">
-        <v>84700</v>
+        <v>16200</v>
       </c>
       <c r="L6" t="n">
-        <v>85500</v>
+        <v>16750</v>
       </c>
       <c r="M6" t="n">
-        <v>84100</v>
+        <v>15560</v>
       </c>
       <c r="N6" t="n">
-        <v>23.37</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>32294487150</v>
+        <v>177323647900</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>-61000</v>
+        <v>-208000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>금리 인상 악재 해소 및 AI 관련 전력 수요 증가 전망. 원전 관련주 연계 상승 기대.</t>
+          <t>미국 광통신 관련주 강세 및 국내 광통신 장비 부족 호재로 인한 긍정적 전망. 2만원 목표 제시 및 긍정적 분위기 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['금리인상', 'AI', '원전']</t>
+          <t>['광통신', '장비부족', '호재']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18630</v>
+        <v>3555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'+0.99%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.21</v>
+        <v>-0.85</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="H7" t="n">
-        <v>10.85</v>
+        <v>2.26</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18570</v>
+        <v>3520</v>
       </c>
       <c r="K7" t="n">
-        <v>18740</v>
+        <v>3730</v>
       </c>
       <c r="L7" t="n">
-        <v>18900</v>
+        <v>3750</v>
       </c>
       <c r="M7" t="n">
-        <v>18580</v>
+        <v>3500</v>
       </c>
       <c r="N7" t="n">
-        <v>10.64</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
-        <v>17837036495</v>
+        <v>3516839383</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>16110</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>-58000</v>
+        <v>-228000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>금리 인상 속 대규모 수주에도 부진한 주가. 대차해지 운동 촉구.</t>
+          <t>상장 폐지 가능성 언급 및 급락세 지속. 차익 실현 매물 출회.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['금리인상', '수주', '대차해지']</t>
+          <t>['상장폐지', '급락', '차익실현']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3517</v>
+        <v>18710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.09%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.85</v>
+        <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="H8" t="n">
-        <v>2.26</v>
+        <v>10.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3520</v>
+        <v>18570</v>
       </c>
       <c r="K8" t="n">
-        <v>3730</v>
+        <v>18740</v>
       </c>
       <c r="L8" t="n">
-        <v>3750</v>
+        <v>18900</v>
       </c>
       <c r="M8" t="n">
-        <v>3510</v>
+        <v>18580</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>10.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3252557025</v>
+        <v>20085513665</v>
       </c>
       <c r="P8" t="n">
-        <v>16110</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>2300</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-228000</v>
+        <v>-58000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장 폐지 가능성 언급 및 급락세 지속. 차익 실현 매물 출회.</t>
+          <t>대규모 수주에도 불구하고 주가 부진에 대한 불만 제기. 금리 인상 및 대차 해지 운동 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장폐지', '급락', '차익실현']</t>
+          <t>['수주', '금리인상', '대차해지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252750</v>
+        <v>253500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="G9" t="n">
-        <v>3143</v>
+        <v>2956</v>
       </c>
       <c r="H9" t="n">
         <v>46.52</v>
@@ -1254,7 +1254,7 @@
         <v>46.56</v>
       </c>
       <c r="O9" t="n">
-        <v>508657100250</v>
+        <v>586781277500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 금리 인상 및 정치적 불확실성 언급. 메모리 수요와 금리 인상 간의 관계에 대한 논의.</t>
+          <t>미국 금리 인상 발표에 따른 불확실성 해소 기대와 정치적 언급 혼재. 반도체 수요 관련 언급 있으나 금리 인상 우려 상존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['금리인상', '메모리수요', '불확실성']</t>
+          <t>['금리인상', '반도체', '불확실성']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13920</v>
+        <v>1747000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.36%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>464</v>
       </c>
       <c r="G10" t="n">
-        <v>189</v>
+        <v>1894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01</v>
+        <v>50.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13970</v>
+        <v>1759000</v>
       </c>
       <c r="K10" t="n">
-        <v>13450</v>
+        <v>1770000</v>
       </c>
       <c r="L10" t="n">
-        <v>13960</v>
+        <v>1785000</v>
       </c>
       <c r="M10" t="n">
-        <v>13410</v>
+        <v>1735000</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>7034366740</v>
+        <v>1129032792500</v>
       </c>
       <c r="P10" t="n">
-        <v>36200</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>8920</v>
+        <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>73000</v>
+        <v>-85000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유가 등락에 따른 변동성 확대. 겨울철 유가 상승 및 전쟁 관련 기대와 하락 우려 공존.</t>
+          <t>미국 금리 인상 후 필라델피아 반도체 지수 상승 및 SK하이닉스 ADR 급등으로 인한 긍정적 전망. 반도체 부족 심화 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유가', '겨울', '전쟁']</t>
+          <t>['금리인상', 'ADR', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8390</v>
+        <v>8400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="H11" t="n">
         <v>26.54</v>
@@ -1438,7 +1438,7 @@
         <v>26.66</v>
       </c>
       <c r="O11" t="n">
-        <v>4125165650</v>
+        <v>4628825185</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>중국 디스플레이 경쟁력 약화 및 높은 부채 비율 언급. 외인 매도세 지속.</t>
+          <t>중국 디스플레이 산업 경쟁 심화, 대규모 부채, 지속적인 악재 및 외국인 매도로 인한 부정적 전망. 희망 없는 좀비 기업으로 평가.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['디스플레이', '중국', '부채']</t>
+          <t>['디스플레이', '부채', '악재']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1736500</v>
+        <v>13770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-1.43%</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" t="n">
+        <v>46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>199</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>13970</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13970</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13410</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>800</v>
-      </c>
-      <c r="F12" t="n">
-        <v>461</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2267</v>
-      </c>
-      <c r="H12" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1770000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1785000</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1736000</v>
-      </c>
-      <c r="N12" t="n">
-        <v>50.2</v>
-      </c>
       <c r="O12" t="n">
-        <v>993429360500</v>
+        <v>8011913885</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>333000</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>-85000</v>
+        <v>73000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 금리 인상 불확실성 해소 기대 속 반도체 부족 심화 전망. 금리 인상 후 폭락 예상도.</t>
+          <t>유가 등락에 따른 변동성 확대. 겨울철 유가 상승 및 전쟁 관련 기대와 하락 우려 공존.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', 'ADR']</t>
+          <t>['유가', '겨울', '전쟁']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260917_09.xlsx
+++ b/data/trending_integrated_20260917_09.xlsx
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10690</v>
+        <v>4085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+7.22%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.58</v>
+        <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="H2" t="n">
-        <v>1.25</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9970</v>
+        <v>3840</v>
       </c>
       <c r="K2" t="n">
-        <v>10280</v>
+        <v>4170</v>
       </c>
       <c r="L2" t="n">
-        <v>11750</v>
+        <v>4500</v>
       </c>
       <c r="M2" t="n">
-        <v>10250</v>
+        <v>3990</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>129420646385</v>
+        <v>102049972743</v>
       </c>
       <c r="P2" t="n">
-        <v>15960</v>
+        <v>6900</v>
       </c>
       <c r="Q2" t="n">
-        <v>3500</v>
+        <v>1738</v>
       </c>
       <c r="R2" t="n">
-        <v>114000</v>
+        <v>-74000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>낙태약 도입 및 탈모 치료 관련 기대감, 치매 테마 영향 가능성 언급. 그러나 개인 매도 및 신뢰 부족 지적.</t>
+          <t>카카오 인수 및 소프트뱅크 투자 관련 기대감으로 인한 급등 가능성 언급. 텐버거(10배 상승) 및 만원 돌파 전망 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '치매테마']</t>
+          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3700</v>
+        <v>10590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+6.22%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>0.58</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>8.01</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
+        <v>9970</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10280</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11750</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10250</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O3" t="n">
+        <v>138454700840</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3500</v>
       </c>
-      <c r="K3" t="n">
-        <v>3590</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4130</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3550</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="O3" t="n">
-        <v>47805819032</v>
-      </c>
-      <c r="P3" t="n">
-        <v>19950</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1913</v>
-      </c>
       <c r="R3" t="n">
-        <v>-55000</v>
+        <v>114000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미래 벤처 투자 관련 언급 있으나, 주가 하락 및 매물량 출회로 인한 부정적 전망. 희망 없는 종목으로 평가.</t>
+          <t>낙태약 및 탈모 치료제 관련 수혜 기대감과 정책주로서의 가능성 언급. 다만, 개인 매물 출현 및 주가 하락 가능성도 제기됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미래벤처', '주가하락', '매물량']</t>
+          <t>['낙태약', '탈모 치료제', '정책주']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4015</v>
+        <v>3655</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.56%</t>
+          <t>'+4.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>443</v>
+        <v>103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>8.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>3500</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>3590</v>
       </c>
       <c r="L4" t="n">
-        <v>4500</v>
+        <v>4130</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>3550</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>8.06</v>
       </c>
       <c r="O4" t="n">
-        <v>97392125706</v>
+        <v>50525813020</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>19950</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>1913</v>
       </c>
       <c r="R4" t="n">
-        <v>-74000</v>
+        <v>-55000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>소프트뱅크 인수 및 카카오 인수 가능성에 대한 높은 기대감. 텐버거 목표 제시 및 거래량 잠김 현상 언급.</t>
+          <t>스페이스X 관련 이슈와 미래 벤처 투자 가능성 언급. 프로그램 매도 및 개인 매수 시 주가 하락 패턴 반복 지적.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['소프트뱅크', '카카오', '텐버거']</t>
+          <t>['스페이스X', '프로그램매도', '미래벤처']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85650</v>
+        <v>85950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.1</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="H5" t="n">
         <v>23.27</v>
@@ -877,7 +877,7 @@
         <v>84700</v>
       </c>
       <c r="L5" t="n">
-        <v>85900</v>
+        <v>86000</v>
       </c>
       <c r="M5" t="n">
         <v>84100</v>
@@ -886,7 +886,7 @@
         <v>23.37</v>
       </c>
       <c r="O5" t="n">
-        <v>41436890350</v>
+        <v>47087538000</v>
       </c>
       <c r="P5" t="n">
         <v>139200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 금리 인상 불확실성 해소 및 AI 시대 전력 수요 증가에 따른 원전 관련 긍정적 전망. 대규모 투자 기대감 언급.</t>
+          <t>AI 투자 대비 전력 부족 가능성 제기. FOMC 악재 소멸 및 금리 인상 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '금리인상', 'AI']</t>
+          <t>['AI', '금리 인상', '원전']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16270</v>
+        <v>18700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>688</v>
+        <v>163</v>
       </c>
       <c r="H6" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K6" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L6" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M6" t="n">
-        <v>15560</v>
+        <v>18580</v>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O6" t="n">
-        <v>177323647900</v>
+        <v>23069338060</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-208000</v>
+        <v>-58000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 강세 및 국내 광통신 장비 부족 호재로 인한 긍정적 전망. 2만원 목표 제시 및 긍정적 분위기 형성.</t>
+          <t>금리 인상으로 인한 불확실성 제거 및 수주 증가 추세 언급. 대차 해지 운동 촉구 및 주가 부양 기대와 하락 우려 공존.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '장비부족', '호재']</t>
+          <t>['금리인상', '수주', '대차해지']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3555</v>
+        <v>16190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.99%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.85</v>
+        <v>2.93</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>185</v>
+        <v>702</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>4.88</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3520</v>
+        <v>16100</v>
       </c>
       <c r="K7" t="n">
-        <v>3730</v>
+        <v>16200</v>
       </c>
       <c r="L7" t="n">
-        <v>3750</v>
+        <v>16750</v>
       </c>
       <c r="M7" t="n">
-        <v>3500</v>
+        <v>15560</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3516839383</v>
+        <v>192471092615</v>
       </c>
       <c r="P7" t="n">
-        <v>16110</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="R7" t="n">
-        <v>-228000</v>
+        <v>-208000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>상장 폐지 가능성 언급 및 급락세 지속. 차익 실현 매물 출회.</t>
+          <t>미국 광통신주 강세에 따른 동반 상승 기대감. 통신 장비 부족 현상 및 2만 원 돌파 전망 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상장폐지', '급락', '차익실현']</t>
+          <t>['광통신', '통신장비', '루멘텀']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18710</v>
+        <v>253750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>427</v>
       </c>
       <c r="G8" t="n">
-        <v>140</v>
+        <v>2697</v>
       </c>
       <c r="H8" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18570</v>
+        <v>253500</v>
       </c>
       <c r="K8" t="n">
-        <v>18740</v>
+        <v>257000</v>
       </c>
       <c r="L8" t="n">
-        <v>18900</v>
+        <v>259000</v>
       </c>
       <c r="M8" t="n">
-        <v>18580</v>
+        <v>252000</v>
       </c>
       <c r="N8" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>20085513665</v>
+        <v>652875076000</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>77100</v>
       </c>
       <c r="R8" t="n">
-        <v>-58000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대규모 수주에도 불구하고 주가 부진에 대한 불만 제기. 금리 인상 및 대차 해지 운동 언급.</t>
+          <t>금리 인상 불확실성 해소 및 반도체 수요 증가 전망. 정치적 이슈와 일부 악재 해소에 대한 언급 포함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '금리인상', '대차해지']</t>
+          <t>['금리인상', '반도체', '악재해소']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253500</v>
+        <v>1746000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="G9" t="n">
-        <v>2956</v>
+        <v>1766</v>
       </c>
       <c r="H9" t="n">
-        <v>46.52</v>
+        <v>50.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>253500</v>
+        <v>1759000</v>
       </c>
       <c r="K9" t="n">
-        <v>257000</v>
+        <v>1770000</v>
       </c>
       <c r="L9" t="n">
-        <v>259000</v>
+        <v>1785000</v>
       </c>
       <c r="M9" t="n">
-        <v>252500</v>
+        <v>1735000</v>
       </c>
       <c r="N9" t="n">
-        <v>46.56</v>
+        <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>586781277500</v>
+        <v>1250092626000</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>77100</v>
+        <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>5000</v>
+        <v>-85000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 금리 인상 발표에 따른 불확실성 해소 기대와 정치적 언급 혼재. 반도체 수요 관련 언급 있으나 금리 인상 우려 상존.</t>
+          <t>미국 증시 반도체주 강세 및 금리 인상에 대한 긍정적 해석. 불확실성 해소로 인한 자사주 매수 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '불확실성']</t>
+          <t>['금리인상', '반도체', 'ADR']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1747000</v>
+        <v>8370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>464</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>1894</v>
+        <v>146</v>
       </c>
       <c r="H10" t="n">
-        <v>50.2</v>
+        <v>26.54</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1759000</v>
+        <v>8470</v>
       </c>
       <c r="K10" t="n">
-        <v>1770000</v>
+        <v>8470</v>
       </c>
       <c r="L10" t="n">
-        <v>1785000</v>
+        <v>8510</v>
       </c>
       <c r="M10" t="n">
-        <v>1735000</v>
+        <v>8360</v>
       </c>
       <c r="N10" t="n">
-        <v>50.2</v>
+        <v>26.66</v>
       </c>
       <c r="O10" t="n">
-        <v>1129032792500</v>
+        <v>5221791915</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R10" t="n">
-        <v>-85000</v>
+        <v>-3000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 금리 인상 후 필라델피아 반도체 지수 상승 및 SK하이닉스 ADR 급등으로 인한 긍정적 전망. 반도체 부족 심화 언급.</t>
+          <t>중국 경쟁 심화 및 높은 부채 비율로 인한 부정적 전망. 외인 매도세 지속 및 주가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금리인상', 'ADR', '반도체']</t>
+          <t>['중국 BOE', '부채', '외인매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8400</v>
+        <v>3475</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.12</v>
+        <v>-0.85</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="H11" t="n">
-        <v>26.54</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8470</v>
+        <v>3520</v>
       </c>
       <c r="K11" t="n">
-        <v>8470</v>
+        <v>3730</v>
       </c>
       <c r="L11" t="n">
-        <v>8510</v>
+        <v>3750</v>
       </c>
       <c r="M11" t="n">
-        <v>8370</v>
+        <v>3460</v>
       </c>
       <c r="N11" t="n">
-        <v>26.66</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>4628825185</v>
+        <v>3905821065</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>16110</v>
       </c>
       <c r="Q11" t="n">
-        <v>8120</v>
+        <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>-3000</v>
+        <v>-228000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>중국 디스플레이 산업 경쟁 심화, 대규모 부채, 지속적인 악재 및 외국인 매도로 인한 부정적 전망. 희망 없는 좀비 기업으로 평가.</t>
+          <t>별다른 소식 없이 급락하며 상장 폐지 가능성 언급. 투자자들의 차익 실현 및 매도 심리 강하게 작용.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['디스플레이', '부채', '악재']</t>
+          <t>['상장폐지', '차익실현', '폭락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13770</v>
+        <v>13630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.43%</t>
+          <t>'-2.43%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H12" t="n">
         <v>0.01</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>8011913885</v>
+        <v>8705749155</v>
       </c>
       <c r="P12" t="n">
         <v>36200</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>유가 등락에 따른 변동성 확대. 겨울철 유가 상승 및 전쟁 관련 기대와 하락 우려 공존.</t>
+          <t>국제 유가 변동성에 따른 주가 등락 예상. 유가 하락 및 조정 후 상승 전망, 전쟁 관련 불확실성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['유가', '겨울', '전쟁']</t>
+          <t>['국제유가', '전쟁', '흥구석유']</t>
         </is>
       </c>
       <c r="X12" t="n">
